--- a/Tagihan/2026/Agustus/Kambitin Raya.xlsx
+++ b/Tagihan/2026/Agustus/Kambitin Raya.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\2026\Agustus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F15B959-DBBE-4EC9-AC1E-B61C318E44F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4AB551-E5AA-43B5-8D2B-D67F88081E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
